--- a/tests/agent_contract/data/H2_number_format.xlsx
+++ b/tests/agent_contract/data/H2_number_format.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,26 +413,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>产品A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>5,935</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
@@ -447,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3299</v>
+        <v>2813</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -463,12 +473,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2,354元</t>
+          <t>2,490</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
@@ -480,7 +490,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3701元</t>
+          <t>3929元</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -495,14 +505,12 @@
           <t>产品A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3,148</t>
-        </is>
+      <c r="B6" t="n">
+        <v>2593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
@@ -514,12 +522,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4971元</t>
+          <t>3899元</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -531,7 +539,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,491</t>
+          <t>2,198元</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -548,7 +556,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5,954</t>
+          <t>5,784</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -565,12 +573,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2570元</t>
+          <t>5,923元</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
@@ -582,7 +590,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3909元</t>
+          <t>49,436元</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -594,34 +602,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>产品A</t>
+          <t>产品B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3,910</t>
+          <t>2,567</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>产品A</t>
+          <t>产品B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>45,693元</t>
+          <t>4163元</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
@@ -633,7 +641,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2,167</t>
+          <t>4,954</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -650,7 +658,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4742元</t>
+          <t>4,076</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -667,12 +675,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3,729</t>
+          <t>5,451元</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
@@ -684,7 +692,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5,371元</t>
+          <t>5817元</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -701,12 +709,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2,999元</t>
+          <t>4,501</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -717,7 +725,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4350</v>
+        <v>3925</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -733,7 +741,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3947元</t>
+          <t>2630元</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -748,12 +756,14 @@
           <t>产品B</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>5899</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3273元</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
@@ -765,12 +775,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5987元</t>
+          <t>2943元</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
@@ -782,7 +792,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3,773</t>
+          <t>5,225元</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -797,8 +807,10 @@
           <t>产品B</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>4151</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3071元</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -814,7 +826,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4317元</t>
+          <t>19,404</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -826,11 +838,13 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>产品B</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>3344</v>
+          <t>产品C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4,976</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -841,46 +855,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>产品C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3,834元</t>
+          <t>2714元</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>产品C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3,355</t>
+          <t>2,378元</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>产品C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10,035元</t>
+          <t>5,073</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -897,7 +911,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2,616元</t>
+          <t>5177元</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -914,7 +928,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5,227</t>
+          <t>3,273</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -931,12 +945,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3,847元</t>
+          <t>2428元</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -948,12 +962,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3782元</t>
+          <t>2,219元</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -965,12 +979,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4,937元</t>
+          <t>2019元</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -980,10 +994,8 @@
           <t>产品C</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3,786元</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4844</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -999,7 +1011,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3,376元</t>
+          <t>2355元</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1014,107 +1026,105 @@
           <t>产品C</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>2401</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>27,544</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>产品C</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2,990</t>
-        </is>
+          <t>产品D</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3043</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>产品C</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2332元</t>
-        </is>
+          <t>产品D</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2495</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2840</v>
+        <v>4496</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2702元</t>
+          <t>2578元</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3,905元</t>
+          <t>5,532元</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20,259</t>
+          <t>4,530元</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1129,8 +1139,10 @@
           <t>产品D</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>4873</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>3,502元</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1144,12 +1156,14 @@
           <t>产品D</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>3583</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2279元</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1175,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2422元</t>
+          <t>2,128元</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1192,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3,869元</t>
+          <t>4,168元</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1207,14 @@
           <t>产品D</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>5320</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>3,915元</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1226,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5,836元</t>
+          <t>3952元</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
@@ -1225,14 +1241,12 @@
           <t>产品D</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>5,726元</t>
-        </is>
+      <c r="B50" t="n">
+        <v>3311</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1256,14 @@
           <t>产品D</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>4205</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3,321</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1275,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3,109</t>
+          <t>3,338</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1292,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2,645</t>
+          <t>3,277</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1292,22 +1308,24 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2684</v>
+        <v>2135</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>产品D</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3567</v>
+          <t>产品E</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>3077元</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1318,28 +1336,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>产品D</t>
+          <t>产品E</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2,010</t>
+          <t>2082元</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>产品D</t>
+          <t>产品E</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2044</v>
+        <v>2070</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1350,12 +1368,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>产品D</t>
+          <t>产品E</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2093元</t>
+          <t>5,050</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1367,12 +1385,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>产品D</t>
+          <t>产品E</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2,012元</t>
+          <t>5,606元</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1384,15 +1402,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>产品D</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>2002</v>
+          <t>产品E</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4,340</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -1402,10 +1422,8 @@
           <t>产品E</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>3,770</t>
-        </is>
+      <c r="B61" t="n">
+        <v>2946</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1421,12 +1439,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2,677元</t>
+          <t>3,831</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
@@ -1436,14 +1454,12 @@
           <t>产品E</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>5,092元</t>
-        </is>
+      <c r="B63" t="n">
+        <v>2329</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
@@ -1453,14 +1469,12 @@
           <t>产品E</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>4,311元</t>
-        </is>
+      <c r="B64" t="n">
+        <v>2348</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1486,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5561元</t>
+          <t>2249元</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1487,12 +1501,14 @@
           <t>产品E</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>3005</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2,032元</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
@@ -1502,14 +1518,12 @@
           <t>产品E</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2,418元</t>
-        </is>
+      <c r="B67" t="n">
+        <v>2003</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1535,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4,284</t>
+          <t>2,011</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1552,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3,800元</t>
+          <t>2013元</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1569,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2,689元</t>
+          <t>2,003元</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1570,44 +1584,12 @@
           <t>产品E</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>4045</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2,010元</t>
+        </is>
       </c>
       <c r="C71" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>产品E</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>3,635</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>产品E</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2,713元</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
